--- a/public/template/template_attachment.xlsx
+++ b/public/template/template_attachment.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\iss dokumen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\hafivah.tahta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA9C4C60-31A5-419B-A2C8-6A86DB00C372}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B76C7D3-32DF-4F27-BDC5-627381CCD9C3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="11325" windowHeight="7890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,12 +20,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Badge Number</t>
-  </si>
-  <si>
-    <t>Full Name</t>
   </si>
   <si>
     <t>Remarks</t>
@@ -132,23 +129,23 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -452,98 +449,83 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18" style="5" customWidth="1"/>
-    <col min="2" max="2" width="25" style="5" customWidth="1"/>
-    <col min="3" max="3" width="37.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20" style="5" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="5"/>
+    <col min="1" max="1" width="18" style="2" customWidth="1"/>
+    <col min="2" max="2" width="37.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20" style="2" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="4"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="6"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
+      <c r="C3" s="1"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="D1:D2"/>
+  <mergeCells count="3">
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
